--- a/docs/iap-tip-products.xlsx
+++ b/docs/iap-tip-products.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AGC导入模板" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="官方模板对照" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摆件映射" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,53 +447,53 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>productId</t>
+          <t>productNo</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>productType</t>
+          <t>productName</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>productDesc</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>defaultLanguage</t>
+          <t>purchaseType</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>defaultLocale</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>country</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>price</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>country</t>
         </is>
       </c>
     </row>
@@ -504,34 +505,36 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>支持 · 心意</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>对开发者的自愿支持，用于应用后续开发与维护（部分将捐赠公益）。不承诺任何祈福效果，也不解锁任何权益。</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>consumable</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>zh-CN</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>支持 · 心意</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>对开发者的自愿支持，用于应用后续开发与维护（部分将捐赠公益）。不承诺任何祈福效果，也不解锁任何权益。</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
+          <t>zh_CN</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
         <v>8</v>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -542,34 +545,36 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>祝愿 · 顺遂</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>对开发者的自愿支持，用于应用后续开发与维护（部分将捐赠公益）。不承诺任何祈福效果，也不解锁任何权益。</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>consumable</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>zh-CN</t>
-        </is>
-      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>祝愿 · 顺遂</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>对开发者的自愿支持，用于应用后续开发与维护（部分将捐赠公益）。不承诺任何祈福效果，也不解锁任何权益。</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
+          <t>zh_CN</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
         <v>18</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -580,34 +585,36 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>福田 · 同行</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>对开发者的自愿支持，用于应用后续开发与维护（部分将捐赠公益）。不承诺任何祈福效果，也不解锁任何权益。</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>consumable</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>zh-CN</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>福田 · 同行</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>对开发者的自愿支持，用于应用后续开发与维护（部分将捐赠公益）。不承诺任何祈福效果，也不解锁任何权益。</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
+          <t>zh_CN</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>88</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -618,34 +625,36 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>殿设 · 聚宝</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>对开发者的自愿支持，用于应用后续开发与维护（部分将捐赠公益）。不承诺任何祈福效果，也不解锁任何权益。</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>consumable</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>zh-CN</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>殿设 · 聚宝</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>对开发者的自愿支持，用于应用后续开发与维护（部分将捐赠公益）。不承诺任何祈福效果，也不解锁任何权益。</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
+          <t>zh_CN</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
         <v>188</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -656,34 +665,36 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>至诚 · 厚爱</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>对开发者的自愿支持，用于应用后续开发与维护（部分将捐赠公益）。不承诺任何祈福效果，也不解锁任何权益。</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>consumable</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>zh-CN</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>至诚 · 厚爱</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>对开发者的自愿支持，用于应用后续开发与维护（部分将捐赠公益）。不承诺任何祈福效果，也不解锁任何权益。</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
+          <t>zh_CN</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>888</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -697,147 +708,290 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="92" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>AGC 打赏五档消耗型商品 · 批量导入说明</t>
+          <t>AGC 控制台「商品管理 → 批量操作 → 导入商品」使用官方「商品模板」填报。</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr"/>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>本文件「商品数据」表用 Connect API 字段名给出数值；导入到官方模板时按下面对照复制。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>本表「AGC导入模板」为英文表头，对应 AGC 商品管理 → 导入 的模板字段。</t>
-        </is>
-      </c>
+      <c r="A3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>如 AGC 下载的官方模板列名/顺序不同，请以官方模板为准，把本表数值复制进对应列。</t>
+          <t>⚠️ 两处值格式坑（上一版报「模板不正确」的根因）：</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr"/>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. purchaseType（商品类型）：官方模板里用【数字】，消耗型 = 0（写成 consumable 会报错）。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>字段说明：</t>
+          <t xml:space="preserve">     0=消耗型 / 2=订阅 / 3=非消耗型。本应用 5 个打赏+摆件商品全部是 0（消耗型）。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  productId     : 商品 ID（不可改名，故 tip_18→tip_18_2、tip_88→tip_88_2）</t>
+          <t xml:space="preserve">  2. defaultLocale（默认语言）：用【下划线】 zh_CN，不是 zh-CN（连字符会报错）。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  productType   : consumable（消耗型）</t>
-        </is>
-      </c>
+      <c r="A8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  status        : 1=上架 / 0=下架</t>
+          <t>字段对照（本文件 → 官方模板列，以你下载的官方模板实际列名为准）：</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  defaultLanguage: zh-CN</t>
+          <t xml:space="preserve">  productNo      → 商品ID / productId（同一应用内不可重复，不可重名）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  name          : 商品名称（中性文案，不含 香/供奉/祈福/解锁权益）</t>
+          <t xml:space="preserve">  purchaseType   → 商品类型（0=消耗型）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  description   : 通用描述（见各单元格）</t>
+          <t xml:space="preserve">  productName    → 商品名称（≤55 字符，不支持 |）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  price         : 人民币定价（元）</t>
+          <t xml:space="preserve">  productDesc    → 商品描述（≤100 字符，不支持 |）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  country       : CN（鸿蒙 IAP 仅支持中国大陆）</t>
+          <t xml:space="preserve">  defaultLocale  → 默认语言（zh_CN）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  country        → CN（鸿蒙 IAP 仅中国大陆）</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>三方一致性（已同步）：</t>
+          <t xml:space="preserve">  currency       → CNY</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  端侧  : entry/.../service/IPaymentService.ets 的 TIP_PRODUCTS</t>
+          <t xml:space="preserve">  price          → 人民币元（8 / 18 / 88 / 188 / 888，具体单元格格式以官方模板为准）</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  云侧  : cloud/donation-record/handler.js 的 PRODUCT_IDS 白名单</t>
-        </is>
-      </c>
+      <c r="A18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AGC   : 以上 5 个商品（tip_8 / tip_18_2 / tip_88_2 / tip_188 / tip_888）</t>
+          <t>步骤：商品管理 → 下载官方模板 → 把「商品数据」5 行按上面对照复制进对应列 → 上传导入。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>提醒：AGC 旧的 tip_18 / tip_88（无 _2 后缀）若仍存在可下架/删除，避免混淆。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       tip_188（殿设 · 聚宝）对应财神殿「聚宝盆」陈设；tip_888（至诚 · 厚爱）对应水晶殿主题，仅改视觉，不承诺祈福效力。</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>提示：若商品已存在，会按 productNo 覆盖名称/描述/价格；商品类型一旦创建不可改。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>商品ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>金额(元)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>解锁的财神殿摆件 / 装扮</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>tip_8</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>灯样式：莲灯 / 琉璃灯；陈设：宫灯</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>tip_18_2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>香炉：三足炉 / 鎏金炉；陈设：金瓶</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>tip_88_2</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>殿宇主题：金辉殿 / 夜殿；陈设：鲜花</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>tip_188</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>陈设：聚宝盆（殿内第四件陈设）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>tip_888</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>殿宇主题：水晶殿（尊享）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>说明：财神殿摆件（灯/香炉/殿宇主题 + 四件陈设）复用打赏 5 档商品，代码已约定「不新建 AGC 商品」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>即：买 tip_8 解锁 ¥8 档摆件，买 tip_188 解锁聚宝盆陈设，买 tip_888 解锁水晶殿主题。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>故 AGC 只需创建这 5 个消耗型商品，无需为摆件单独建商品（另建会导致 1001860007 商品未发布）。</t>
         </is>
       </c>
     </row>

--- a/docs/iap-tip-products.xlsx
+++ b/docs/iap-tip-products.xlsx
@@ -442,56 +442,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>productNo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>productName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>productDesc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>purchaseType</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>defaultLocale</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -500,200 +506,450 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>打赏</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>tip_8</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>支持 · 心意</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>对开发者的自愿支持，用于应用后续开发与维护（部分将捐赠公益）。不承诺任何祈福效果，也不解锁任何权益。</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>consumable</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>zh_CN</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>打赏</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>tip_18_2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>祝愿 · 顺遂</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>对开发者的自愿支持，用于应用后续开发与维护（部分将捐赠公益）。不承诺任何祈福效果，也不解锁任何权益。</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>consumable</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>zh_CN</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="I3" s="2" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>打赏</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>tip_88_2</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>福田 · 同行</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>对开发者的自愿支持，用于应用后续开发与维护（部分将捐赠公益）。不承诺任何祈福效果，也不解锁任何权益。</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>consumable</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>zh_CN</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>打赏</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>tip_188</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>殿设 · 聚宝</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>厚意 · 圆满</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>对开发者的自愿支持，用于应用后续开发与维护（部分将捐赠公益）。不承诺任何祈福效果，也不解锁任何权益。</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>consumable</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>zh_CN</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="I5" s="2" t="n">
         <v>188</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>打赏</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>tip_888</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>至诚 · 厚爱</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>对开发者的自愿支持，用于应用后续开发与维护（部分将捐赠公益）。不承诺任何祈福效果，也不解锁任何权益。</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>consumable</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>zh_CN</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="I6" s="2" t="n">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>装扮</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>decor_8</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>灯样式 · 莲灯 / 琉璃灯</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>解锁财神殿内对应装扮/陈设，仅改变殿内视觉效果。不涉及任何祈福效力，不承诺任何效果。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>zh_CN</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>装扮</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>decor_18</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>香炉 · 三足炉 / 鎏金炉</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>解锁财神殿内对应装扮/陈设，仅改变殿内视觉效果。不涉及任何祈福效力，不承诺任何效果。</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>zh_CN</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>装扮</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>decor_88</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>殿宇 · 金辉殿 / 夜殿</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>解锁财神殿内对应装扮/陈设，仅改变殿内视觉效果。不涉及任何祈福效力，不承诺任何效果。</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>zh_CN</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>装扮</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>decor_188</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>陈设 · 聚宝盆</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>解锁财神殿内对应装扮/陈设，仅改变殿内视觉效果。不涉及任何祈福效力，不承诺任何效果。</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>zh_CN</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>装扮</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>decor_888</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>殿宇 · 水晶殿（尊享）</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>解锁财神殿内对应装扮/陈设，仅改变殿内视觉效果。不涉及任何祈福效力，不承诺任何效果。</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>zh_CN</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>888</v>
       </c>
     </row>
@@ -724,7 +980,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>本文件「商品数据」表用 Connect API 字段名给出数值；导入到官方模板时按下面对照复制。</t>
+          <t>本文件「商品数据」表用 Connect API 字段名给出数值；导入官方模板时按下面对照复制（「分类」列仅供人阅读，不导入）。</t>
         </is>
       </c>
     </row>
@@ -734,28 +990,28 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>⚠️ 两处值格式坑（上一版报「模板不正确」的根因）：</t>
+          <t>⚠️ 两个值格式坑（上一版报「模板不正确」的根因）：</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. purchaseType（商品类型）：官方模板里用【数字】，消耗型 = 0（写成 consumable 会报错）。</t>
+          <t xml:space="preserve">  1. 商品类型：官方模板用【数字】，消耗型 = 0（写成 consumable 会报错）。0=消耗型 / 2=订阅 / 3=非消耗型。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">     0=消耗型 / 2=订阅 / 3=非消耗型。本应用 5 个打赏+摆件商品全部是 0（消耗型）。</t>
+          <t xml:space="preserve">     本应用 10 个商品（打赏 5 + 装扮 5）全部是 0（消耗型）。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. defaultLocale（默认语言）：用【下划线】 zh_CN，不是 zh-CN（连字符会报错）。</t>
+          <t xml:space="preserve">  2. 默认语言：用【下划线】 zh_CN，不是 zh-CN（连字符会报错）。</t>
         </is>
       </c>
     </row>
@@ -821,7 +1077,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  price          → 人民币元（8 / 18 / 88 / 188 / 888，具体单元格格式以官方模板为准）</t>
+          <t xml:space="preserve">  price          → 人民币元（具体单元格格式以官方模板为准）</t>
         </is>
       </c>
     </row>
@@ -831,14 +1087,14 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>步骤：商品管理 → 下载官方模板 → 把「商品数据」5 行按上面对照复制进对应列 → 上传导入。</t>
+          <t>步骤：商品管理 → 下载官方模板 → 把「商品数据」10 行复制进对应列 → 上传导入。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>提示：若商品已存在，会按 productNo 覆盖名称/描述/价格；商品类型一旦创建不可改。</t>
+          <t>提示：已存在的商品会按 productNo 覆盖名称/描述/价格；商品类型创建后不可改。</t>
         </is>
       </c>
     </row>
@@ -853,18 +1109,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>商品ID</t>
+          <t>装扮商品ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -881,7 +1137,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>tip_8</t>
+          <t>decor_8</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -898,7 +1154,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>tip_18_2</t>
+          <t>decor_18</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -915,7 +1171,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>tip_88_2</t>
+          <t>decor_88</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -932,7 +1188,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>tip_188</t>
+          <t>decor_188</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -942,14 +1198,14 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>陈设：聚宝盆（殿内第四件陈设）</t>
+          <t>陈设：聚宝盆</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>tip_888</t>
+          <t>decor_888</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -973,7 +1229,7 @@
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>说明：财神殿摆件（灯/香炉/殿宇主题 + 四件陈设）复用打赏 5 档商品，代码已约定「不新建 AGC 商品」。</t>
+          <t>说明：装扮/陈设是独立消耗型商品（decor_*），与打赏（tip_*）完全分开；购买只解锁视觉、不进公益榜。</t>
         </is>
       </c>
     </row>
@@ -982,16 +1238,7 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>即：买 tip_8 解锁 ¥8 档摆件，买 tip_188 解锁聚宝盆陈设，买 tip_888 解锁水晶殿主题。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>故 AGC 只需创建这 5 个消耗型商品，无需为摆件单独建商品（另建会导致 1001860007 商品未发布）。</t>
+          <t>打赏 tip_* 现为纯赠与，不再解锁任何摆件。</t>
         </is>
       </c>
     </row>
